--- a/Normalization/Author.xlsx
+++ b/Normalization/Author.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\databaseproject-G9\Normalization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F66147-AC44-4064-B60D-684B321CA79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894280FB-F7EF-407A-A25B-36D52B7B0030}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,17 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -65,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="550">
   <si>
     <t>小魚兒不愛花無缺</t>
   </si>
@@ -1702,9 +1691,6 @@
   <si>
     <t>作者</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aipi</t>
   </si>
   <si>
     <t>李柏青</t>
@@ -1793,8 +1779,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}" name="工作表1__210122" displayName="工作表1__210122" ref="A1:B551" totalsRowShown="0">
-  <autoFilter ref="A1:B551" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}" name="工作表1__210122" displayName="工作表1__210122" ref="A1:B550" totalsRowShown="0">
+  <autoFilter ref="A1:B550" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}"/>
   <tableColumns count="2">
     <tableColumn id="14" xr3:uid="{46B9DB32-F916-48A1-914E-F861B7933414}" name="作者代號"/>
     <tableColumn id="2" xr3:uid="{D69DDAD9-7089-4BC9-81EE-03C28CACB005}" name="作者"/>
@@ -2098,7 +2084,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>545</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2106,7 +2092,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>513</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2114,7 +2100,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>340</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2122,7 +2108,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>457</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2130,7 +2116,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2138,7 +2124,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>519</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2146,7 +2132,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2154,7 +2140,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>463</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -2162,7 +2148,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>421</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -2170,7 +2156,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -2178,7 +2164,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -2186,7 +2172,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>431</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2194,7 +2180,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>341</v>
+        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2202,7 +2188,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>516</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -2210,7 +2196,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>442</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -2218,7 +2204,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>490</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2226,7 +2212,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>335</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -2234,7 +2220,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -2242,7 +2228,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>536</v>
+        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -2250,7 +2236,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>395</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2258,7 +2244,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>305</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -2266,7 +2252,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>533</v>
+        <v>460</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -2274,7 +2260,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>460</v>
+        <v>393</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2282,7 +2268,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -2290,7 +2276,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>374</v>
+        <v>476</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -2298,7 +2284,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>476</v>
+        <v>534</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -2306,7 +2292,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>534</v>
+        <v>381</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -2314,7 +2300,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>381</v>
+        <v>475</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -2322,7 +2308,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>475</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -2330,7 +2316,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -2338,7 +2324,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>537</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -2346,7 +2332,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>304</v>
+        <v>145</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -2354,7 +2340,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -2362,7 +2348,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>144</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -2370,7 +2356,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>378</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -2378,7 +2364,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>143</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -2386,7 +2372,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>291</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -2394,7 +2380,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -2402,7 +2388,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>142</v>
+        <v>326</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -2410,7 +2396,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2418,7 +2404,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>297</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2426,7 +2412,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2434,7 +2420,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>506</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2442,7 +2428,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>356</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2450,7 +2436,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>356</v>
+        <v>485</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2458,7 +2444,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>485</v>
+        <v>520</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2466,7 +2452,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>520</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2474,7 +2460,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>280</v>
+        <v>467</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2482,7 +2468,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>467</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2490,7 +2476,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2498,7 +2484,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>135</v>
+        <v>484</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2506,7 +2492,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>484</v>
+        <v>500</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2514,7 +2500,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>500</v>
+        <v>456</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2522,7 +2508,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>456</v>
+        <v>303</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2530,7 +2516,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2538,7 +2524,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2546,7 +2532,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>322</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2554,7 +2540,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>498</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2562,7 +2548,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>405</v>
+        <v>278</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2570,7 +2556,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2578,7 +2564,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>287</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2586,7 +2572,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>141</v>
+        <v>276</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2594,7 +2580,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>276</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2602,7 +2588,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>137</v>
+        <v>388</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2610,7 +2596,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>388</v>
+        <v>487</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2618,7 +2604,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>487</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2626,7 +2612,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2634,7 +2620,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2642,7 +2628,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>138</v>
+        <v>384</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2650,7 +2636,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2658,7 +2644,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2666,7 +2652,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>386</v>
+        <v>288</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2674,7 +2660,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>288</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2682,7 +2668,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>499</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2690,7 +2676,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2698,7 +2684,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>299</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2706,7 +2692,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>299</v>
+        <v>529</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2714,7 +2700,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>529</v>
+        <v>328</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2722,7 +2708,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>328</v>
+        <v>175</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2730,7 +2716,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2738,7 +2724,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>309</v>
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2746,7 +2732,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2754,7 +2740,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2762,7 +2748,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>392</v>
+        <v>302</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2770,7 +2756,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>302</v>
+        <v>172</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2778,7 +2764,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>172</v>
+        <v>481</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2786,7 +2772,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>481</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2794,7 +2780,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2802,7 +2788,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>441</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2810,7 +2796,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2818,7 +2804,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>363</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2826,7 +2812,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>363</v>
+        <v>129</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2834,7 +2820,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2842,7 +2828,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
+        <v>390</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2850,7 +2836,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2858,7 +2844,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2866,7 +2852,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2874,7 +2860,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>289</v>
+        <v>188</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2882,7 +2868,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>188</v>
+        <v>370</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2890,7 +2876,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>370</v>
+        <v>151</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2898,7 +2884,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2906,7 +2892,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>130</v>
+        <v>274</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2914,7 +2900,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2922,7 +2908,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>301</v>
+        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2930,7 +2916,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2938,7 +2924,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>275</v>
+        <v>501</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2946,7 +2932,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>501</v>
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2954,7 +2940,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2962,7 +2948,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>134</v>
+        <v>418</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2970,7 +2956,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>418</v>
+        <v>81</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2978,7 +2964,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>81</v>
+        <v>415</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2986,7 +2972,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>415</v>
+        <v>202</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2994,7 +2980,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>202</v>
+        <v>293</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -3002,7 +2988,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>293</v>
+        <v>524</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -3010,7 +2996,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>524</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -3018,7 +3004,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>54</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -3026,7 +3012,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>312</v>
+        <v>382</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -3034,7 +3020,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -3042,7 +3028,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -3050,7 +3036,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>429</v>
+        <v>372</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -3058,7 +3044,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>372</v>
+        <v>445</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -3066,7 +3052,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>445</v>
+        <v>56</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -3074,7 +3060,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -3082,7 +3068,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>281</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -3090,7 +3076,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>94</v>
+        <v>470</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -3098,7 +3084,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>470</v>
+        <v>159</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -3106,7 +3092,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>159</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -3114,7 +3100,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>10</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -3122,7 +3108,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>285</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -3130,7 +3116,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>80</v>
+        <v>430</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3124,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>430</v>
+        <v>358</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3146,7 +3132,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>358</v>
+        <v>119</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3154,7 +3140,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>468</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3162,7 +3148,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>468</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3170,7 +3156,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>347</v>
+        <v>279</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3178,7 +3164,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>279</v>
+        <v>91</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3186,7 +3172,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>91</v>
+        <v>486</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3194,7 +3180,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>486</v>
+        <v>319</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3202,7 +3188,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>319</v>
+        <v>530</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3210,7 +3196,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>530</v>
+        <v>60</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3218,7 +3204,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>60</v>
+        <v>361</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3226,7 +3212,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3234,7 +3220,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3242,7 +3228,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3236,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>284</v>
+        <v>120</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3258,7 +3244,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3266,7 +3252,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>198</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3274,7 +3260,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>198</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3282,7 +3268,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3290,7 +3276,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>273</v>
+        <v>380</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3298,7 +3284,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>380</v>
+        <v>518</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3306,7 +3292,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>518</v>
+        <v>193</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3314,7 +3300,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>193</v>
+        <v>109</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3322,7 +3308,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>109</v>
+        <v>515</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3330,7 +3316,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3338,7 +3324,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>535</v>
+        <v>277</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3346,7 +3332,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>277</v>
+        <v>66</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3354,7 +3340,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>66</v>
+        <v>338</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3362,7 +3348,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>338</v>
+        <v>163</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3370,7 +3356,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>375</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3378,7 +3364,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>375</v>
+        <v>502</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3386,7 +3372,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3394,7 +3380,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>483</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3402,7 +3388,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3410,7 +3396,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>18</v>
+        <v>199</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3418,7 +3404,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3426,7 +3412,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>140</v>
+        <v>523</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3434,7 +3420,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>523</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3442,7 +3428,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>411</v>
+        <v>477</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3450,7 +3436,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3458,7 +3444,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>283</v>
+        <v>436</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3466,7 +3452,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3474,7 +3460,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>439</v>
+        <v>290</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3482,7 +3468,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>290</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3490,7 +3476,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>38</v>
+        <v>282</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3498,7 +3484,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>282</v>
+        <v>36</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3506,7 +3492,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3514,7 +3500,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3522,7 +3508,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3530,7 +3516,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3538,7 +3524,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3546,7 +3532,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3554,7 +3540,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3562,7 +3548,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>344</v>
+        <v>178</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3570,7 +3556,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>178</v>
+        <v>296</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3578,7 +3564,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>296</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3586,7 +3572,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3594,7 +3580,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>17</v>
+        <v>343</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3602,7 +3588,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>343</v>
+        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3610,7 +3596,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>546</v>
+        <v>323</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3618,7 +3604,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>323</v>
+        <v>44</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3626,7 +3612,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>397</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3634,7 +3620,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>397</v>
+        <v>295</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3642,7 +3628,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>295</v>
+        <v>542</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3650,7 +3636,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>542</v>
+        <v>396</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3658,7 +3644,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>396</v>
+        <v>29</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3666,7 +3652,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3674,7 +3660,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>87</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3682,7 +3668,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>447</v>
+        <v>200</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3690,7 +3676,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>362</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3698,7 +3684,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>362</v>
+        <v>503</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3706,7 +3692,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>503</v>
+        <v>294</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3714,7 +3700,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>294</v>
+        <v>42</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3722,7 +3708,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3730,7 +3716,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>162</v>
+        <v>348</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3738,7 +3724,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>348</v>
+        <v>260</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3746,7 +3732,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>260</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3754,7 +3740,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3762,7 +3748,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>317</v>
+        <v>258</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3770,7 +3756,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3778,7 +3764,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>262</v>
+        <v>353</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3786,7 +3772,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>353</v>
+        <v>261</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3794,7 +3780,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>261</v>
+        <v>444</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3802,7 +3788,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>444</v>
+        <v>241</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3810,7 +3796,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3818,7 +3804,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>264</v>
+        <v>57</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3826,7 +3812,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>57</v>
+        <v>509</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3834,7 +3820,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>509</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3842,7 +3828,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3850,7 +3836,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3858,7 +3844,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3866,7 +3852,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>355</v>
+        <v>438</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3874,7 +3860,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>438</v>
+        <v>376</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3882,7 +3868,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>376</v>
+        <v>408</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3890,7 +3876,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>408</v>
+        <v>161</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3898,7 +3884,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>161</v>
+        <v>399</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3906,7 +3892,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>399</v>
+        <v>426</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3914,7 +3900,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3922,7 +3908,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>400</v>
+        <v>236</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3930,7 +3916,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>236</v>
+        <v>406</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3938,7 +3924,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>406</v>
+        <v>245</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3946,7 +3932,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>245</v>
+        <v>517</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3954,7 +3940,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>517</v>
+        <v>85</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3962,7 +3948,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3970,7 +3956,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3978,7 +3964,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>33</v>
+        <v>233</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3986,7 +3972,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>233</v>
+        <v>313</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3994,7 +3980,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -4002,7 +3988,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>337</v>
+        <v>156</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -4010,7 +3996,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -4018,7 +4004,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -4026,7 +4012,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>21</v>
+        <v>462</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -4034,7 +4020,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -4042,7 +4028,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>471</v>
+        <v>176</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -4050,7 +4036,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>176</v>
+        <v>342</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -4058,7 +4044,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -4066,7 +4052,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>367</v>
+        <v>185</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -4074,7 +4060,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>185</v>
+        <v>320</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -4082,7 +4068,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>320</v>
+        <v>95</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -4090,7 +4076,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>95</v>
+        <v>58</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -4098,7 +4084,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>58</v>
+        <v>232</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -4106,7 +4092,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>232</v>
+        <v>465</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -4114,7 +4100,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>465</v>
+        <v>357</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -4122,7 +4108,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>357</v>
+        <v>522</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -4130,7 +4116,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>522</v>
+        <v>179</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4138,7 +4124,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>179</v>
+        <v>473</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4146,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>473</v>
+        <v>201</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4154,7 +4140,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4162,7 +4148,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>164</v>
+        <v>440</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4170,7 +4156,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>440</v>
+        <v>160</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -4178,7 +4164,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>160</v>
+        <v>318</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -4186,7 +4172,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>318</v>
+        <v>394</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -4194,7 +4180,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>394</v>
+        <v>89</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -4202,7 +4188,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>89</v>
+        <v>246</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -4210,7 +4196,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -4218,7 +4204,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>19</v>
+        <v>271</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -4226,7 +4212,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>271</v>
+        <v>539</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -4234,7 +4220,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>539</v>
+        <v>489</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -4242,7 +4228,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>489</v>
+        <v>422</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -4250,7 +4236,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>422</v>
+        <v>334</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -4258,7 +4244,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>334</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -4266,7 +4252,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -4274,7 +4260,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>102</v>
+        <v>389</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -4282,7 +4268,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>389</v>
+        <v>73</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -4290,7 +4276,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>73</v>
+        <v>371</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -4298,7 +4284,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>371</v>
+        <v>14</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -4306,7 +4292,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>14</v>
+        <v>240</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -4314,7 +4300,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>240</v>
+        <v>49</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -4322,7 +4308,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>49</v>
+        <v>497</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -4330,7 +4316,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>497</v>
+        <v>75</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -4338,7 +4324,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>75</v>
+        <v>507</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -4346,7 +4332,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>507</v>
+        <v>68</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -4354,7 +4340,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>68</v>
+        <v>242</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -4362,7 +4348,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -4370,7 +4356,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -4378,7 +4364,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>257</v>
+        <v>23</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -4386,7 +4372,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>23</v>
+        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
@@ -4394,7 +4380,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>540</v>
+        <v>420</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
@@ -4402,7 +4388,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>420</v>
+        <v>238</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
@@ -4410,7 +4396,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
@@ -4418,7 +4404,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>128</v>
+        <v>423</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
@@ -4426,7 +4412,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>423</v>
+        <v>118</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
@@ -4434,7 +4420,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -4442,7 +4428,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>8</v>
+        <v>360</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -4450,7 +4436,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>360</v>
+        <v>62</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -4458,7 +4444,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>62</v>
+        <v>154</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
@@ -4466,7 +4452,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
@@ -4474,7 +4460,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>235</v>
+        <v>272</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -4482,7 +4468,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>272</v>
+        <v>67</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -4490,7 +4476,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -4498,7 +4484,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -4506,7 +4492,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>105</v>
+        <v>321</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -4514,7 +4500,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>321</v>
+        <v>113</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -4522,7 +4508,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>113</v>
+        <v>514</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -4530,7 +4516,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>514</v>
+        <v>195</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -4538,7 +4524,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>195</v>
+        <v>78</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -4546,7 +4532,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -4554,7 +4540,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>234</v>
+        <v>97</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -4562,7 +4548,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>97</v>
+        <v>330</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -4570,7 +4556,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -4578,7 +4564,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>329</v>
+        <v>437</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -4586,7 +4572,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>437</v>
+        <v>308</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -4594,7 +4580,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>308</v>
+        <v>74</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -4602,7 +4588,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -4610,7 +4596,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -4618,7 +4604,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>15</v>
+        <v>192</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -4626,7 +4612,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>192</v>
+        <v>82</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -4634,7 +4620,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>82</v>
+        <v>433</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -4642,7 +4628,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>433</v>
+        <v>331</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -4650,7 +4636,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -4658,7 +4644,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -4666,7 +4652,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>346</v>
+        <v>148</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -4674,7 +4660,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>148</v>
+        <v>237</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -4682,7 +4668,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -4690,7 +4676,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>239</v>
+        <v>6</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -4698,7 +4684,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -4706,7 +4692,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>7</v>
+        <v>122</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -4714,7 +4700,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>122</v>
+        <v>270</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -4722,7 +4708,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>270</v>
+        <v>434</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -4730,7 +4716,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>434</v>
+        <v>269</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -4738,7 +4724,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>269</v>
+        <v>383</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
@@ -4746,7 +4732,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>383</v>
+        <v>254</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
@@ -4754,7 +4740,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>254</v>
+        <v>398</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -4762,7 +4748,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>398</v>
+        <v>458</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
@@ -4770,7 +4756,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>458</v>
+        <v>153</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
@@ -4778,7 +4764,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>153</v>
+        <v>77</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
@@ -4786,7 +4772,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
@@ -4794,7 +4780,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>173</v>
+        <v>526</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
@@ -4802,7 +4788,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>526</v>
+        <v>443</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
@@ -4810,7 +4796,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>443</v>
+        <v>387</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
@@ -4818,7 +4804,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>387</v>
+        <v>314</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
@@ -4826,7 +4812,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
@@ -4834,7 +4820,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>268</v>
+        <v>187</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
@@ -4842,7 +4828,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>187</v>
+        <v>252</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
@@ -4850,7 +4836,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>252</v>
+        <v>401</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
@@ -4858,7 +4844,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>401</v>
+        <v>244</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -4866,7 +4852,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>244</v>
+        <v>453</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -4874,7 +4860,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>453</v>
+        <v>243</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -4882,7 +4868,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>243</v>
+        <v>25</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -4890,7 +4876,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>25</v>
+        <v>546</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -4898,7 +4884,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>547</v>
+        <v>505</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -4906,7 +4892,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>505</v>
+        <v>117</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -4914,7 +4900,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -4922,7 +4908,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -4930,7 +4916,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -4938,7 +4924,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -4946,7 +4932,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -4954,7 +4940,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -4962,7 +4948,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>64</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -4970,7 +4956,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>1</v>
+        <v>265</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -4978,7 +4964,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>265</v>
+        <v>310</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -4986,7 +4972,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -4994,7 +4980,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>332</v>
+        <v>409</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -5002,7 +4988,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>409</v>
+        <v>496</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -5010,7 +4996,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>496</v>
+        <v>407</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -5018,7 +5004,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>407</v>
+        <v>79</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -5026,7 +5012,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -5034,7 +5020,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>114</v>
+        <v>413</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -5042,7 +5028,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>413</v>
+        <v>108</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -5050,7 +5036,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -5058,7 +5044,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>180</v>
+        <v>531</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -5066,7 +5052,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>531</v>
+        <v>100</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -5074,7 +5060,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -5082,7 +5068,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -5090,7 +5076,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -5098,7 +5084,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>256</v>
+        <v>419</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -5106,7 +5092,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>419</v>
+        <v>369</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -5114,7 +5100,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>369</v>
+        <v>253</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -5122,7 +5108,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -5130,7 +5116,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -5138,7 +5124,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>171</v>
+        <v>366</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -5146,7 +5132,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>366</v>
+        <v>84</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -5154,7 +5140,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>84</v>
+        <v>259</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -5162,7 +5148,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -5170,7 +5156,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>247</v>
+        <v>474</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -5178,7 +5164,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -5186,7 +5172,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>493</v>
+        <v>32</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -5194,7 +5180,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -5202,7 +5188,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>2</v>
+        <v>469</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -5210,7 +5196,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -5218,7 +5204,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>461</v>
+        <v>65</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -5226,7 +5212,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>65</v>
+        <v>214</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -5234,7 +5220,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -5242,7 +5228,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>224</v>
+        <v>525</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -5250,7 +5236,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>525</v>
+        <v>203</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -5258,7 +5244,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>203</v>
+        <v>325</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -5266,7 +5252,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>325</v>
+        <v>454</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -5274,7 +5260,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>454</v>
+        <v>11</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -5282,7 +5268,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>11</v>
+        <v>464</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -5290,7 +5276,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>464</v>
+        <v>352</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -5298,7 +5284,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>352</v>
+        <v>55</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -5306,7 +5292,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>55</v>
+        <v>482</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -5314,7 +5300,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>482</v>
+        <v>98</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -5322,7 +5308,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -5330,7 +5316,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -5338,7 +5324,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>103</v>
+        <v>488</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -5346,7 +5332,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>488</v>
+        <v>528</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -5354,7 +5340,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>528</v>
+        <v>324</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -5362,7 +5348,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>324</v>
+        <v>223</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -5370,7 +5356,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>223</v>
+        <v>166</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -5378,7 +5364,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>166</v>
+        <v>512</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -5386,7 +5372,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>512</v>
+        <v>70</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -5394,7 +5380,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>70</v>
+        <v>541</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -5402,7 +5388,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>541</v>
+        <v>510</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -5410,7 +5396,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>510</v>
+        <v>4</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -5418,7 +5404,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>4</v>
+        <v>452</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -5426,7 +5412,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>452</v>
+        <v>480</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -5434,7 +5420,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -5442,7 +5428,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -5450,7 +5436,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>455</v>
+        <v>221</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -5458,7 +5444,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>221</v>
+        <v>377</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -5466,7 +5452,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>377</v>
+        <v>472</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -5474,7 +5460,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -5482,7 +5468,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>448</v>
+        <v>350</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
@@ -5490,7 +5476,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>350</v>
+        <v>190</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -5498,7 +5484,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>190</v>
+        <v>76</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
@@ -5506,7 +5492,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>76</v>
+        <v>491</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
@@ -5514,7 +5500,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
@@ -5522,7 +5508,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>494</v>
+        <v>227</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -5530,7 +5516,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>227</v>
+        <v>414</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -5538,7 +5524,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>414</v>
+        <v>222</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -5546,7 +5532,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -5554,7 +5540,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
@@ -5562,7 +5548,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>96</v>
+        <v>183</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -5570,7 +5556,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>183</v>
+        <v>63</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -5578,7 +5564,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>63</v>
+        <v>404</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -5586,7 +5572,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>404</v>
+        <v>189</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -5594,7 +5580,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>189</v>
+        <v>495</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -5602,7 +5588,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>495</v>
+        <v>336</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -5610,7 +5596,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>336</v>
+        <v>170</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -5618,7 +5604,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>170</v>
+        <v>351</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -5626,7 +5612,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -5634,7 +5620,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>359</v>
+        <v>152</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -5642,7 +5628,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>152</v>
+        <v>217</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
@@ -5650,7 +5636,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
@@ -5658,7 +5644,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>225</v>
+        <v>365</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
@@ -5666,7 +5652,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>365</v>
+        <v>182</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
@@ -5674,7 +5660,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
@@ -5682,7 +5668,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>167</v>
+        <v>339</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
@@ -5690,7 +5676,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>339</v>
+        <v>547</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -5698,7 +5684,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>548</v>
+        <v>104</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -5706,7 +5692,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>104</v>
+        <v>174</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -5714,7 +5700,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
@@ -5722,7 +5708,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
@@ -5730,7 +5716,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>88</v>
+        <v>428</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
@@ -5738,7 +5724,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>428</v>
+        <v>106</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
@@ -5746,7 +5732,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>106</v>
+        <v>155</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
@@ -5754,7 +5740,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>155</v>
+        <v>220</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
@@ -5762,7 +5748,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>220</v>
+        <v>333</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
@@ -5770,7 +5756,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>333</v>
+        <v>228</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
@@ -5778,7 +5764,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>228</v>
+        <v>379</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
@@ -5786,7 +5772,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>379</v>
+        <v>121</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
@@ -5794,7 +5780,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
@@ -5802,7 +5788,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>31</v>
+        <v>165</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
@@ -5810,7 +5796,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
@@ -5818,7 +5804,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>112</v>
+        <v>230</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
@@ -5826,7 +5812,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
@@ -5834,7 +5820,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -5842,7 +5828,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
@@ -5850,7 +5836,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>50</v>
+        <v>315</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
@@ -5858,7 +5844,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>315</v>
+        <v>229</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
@@ -5866,7 +5852,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>229</v>
+        <v>37</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
@@ -5874,7 +5860,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>37</v>
+        <v>479</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
@@ -5882,7 +5868,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>479</v>
+        <v>184</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
@@ -5890,7 +5876,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
@@ -5898,7 +5884,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
@@ -5906,7 +5892,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>34</v>
+        <v>548</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -5914,7 +5900,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>549</v>
+        <v>311</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
@@ -5922,7 +5908,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>311</v>
+        <v>450</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
@@ -5930,7 +5916,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>450</v>
+        <v>412</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
@@ -5938,7 +5924,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>412</v>
+        <v>16</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
@@ -5946,7 +5932,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>16</v>
+        <v>219</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
@@ -5954,7 +5940,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>219</v>
+        <v>424</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
@@ -5962,7 +5948,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>424</v>
+        <v>169</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
@@ -5970,7 +5956,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>169</v>
+        <v>511</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
@@ -5978,7 +5964,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>511</v>
+        <v>149</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
@@ -5986,7 +5972,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>149</v>
+        <v>504</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
@@ -5994,7 +5980,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>504</v>
+        <v>123</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
@@ -6002,7 +5988,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
@@ -6010,7 +5996,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>111</v>
+        <v>216</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
@@ -6018,7 +6004,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>216</v>
+        <v>425</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
@@ -6026,7 +6012,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>425</v>
+        <v>69</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
@@ -6034,7 +6020,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
@@ -6042,7 +6028,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>218</v>
+        <v>28</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
@@ -6050,7 +6036,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
@@ -6058,7 +6044,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
@@ -6066,7 +6052,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
@@ -6074,7 +6060,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
@@ -6082,7 +6068,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
@@ -6090,7 +6076,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
@@ -6098,7 +6084,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>427</v>
+        <v>206</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
@@ -6106,7 +6092,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>206</v>
+        <v>22</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
@@ -6114,7 +6100,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
@@ -6122,7 +6108,7 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>385</v>
+        <v>99</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.25">
@@ -6130,7 +6116,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.25">
@@ -6138,7 +6124,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="s">
-        <v>59</v>
+        <v>478</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.25">
@@ -6146,7 +6132,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>478</v>
+        <v>127</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.25">
@@ -6154,7 +6140,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>127</v>
+        <v>20</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.25">
@@ -6162,7 +6148,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>20</v>
+        <v>549</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.25">
@@ -6170,7 +6156,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>550</v>
+        <v>459</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.25">
@@ -6178,7 +6164,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="s">
-        <v>459</v>
+        <v>41</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.25">
@@ -6186,7 +6172,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.25">
@@ -6194,7 +6180,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>48</v>
+        <v>368</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.25">
@@ -6202,7 +6188,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="s">
-        <v>368</v>
+        <v>30</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.25">
@@ -6210,7 +6196,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>30</v>
+        <v>449</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.25">
@@ -6218,7 +6204,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>449</v>
+        <v>208</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.25">
@@ -6226,7 +6212,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.25">
@@ -6234,7 +6220,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="s">
-        <v>207</v>
+        <v>345</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.25">
@@ -6242,7 +6228,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>345</v>
+        <v>416</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.25">
@@ -6250,7 +6236,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>416</v>
+        <v>126</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.25">
@@ -6258,7 +6244,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="s">
-        <v>126</v>
+        <v>327</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.25">
@@ -6266,7 +6252,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="s">
-        <v>327</v>
+        <v>521</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.25">
@@ -6274,7 +6260,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="s">
-        <v>521</v>
+        <v>124</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.25">
@@ -6282,7 +6268,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="s">
-        <v>124</v>
+        <v>446</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.25">
@@ -6290,7 +6276,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="s">
-        <v>446</v>
+        <v>213</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.25">
@@ -6298,7 +6284,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="s">
-        <v>213</v>
+        <v>391</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.25">
@@ -6306,7 +6292,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="s">
-        <v>391</v>
+        <v>53</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.25">
@@ -6314,7 +6300,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="s">
-        <v>53</v>
+        <v>432</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.25">
@@ -6322,7 +6308,7 @@
         <v>531</v>
       </c>
       <c r="B532" t="s">
-        <v>432</v>
+        <v>39</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.25">
@@ -6330,7 +6316,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="s">
-        <v>39</v>
+        <v>181</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.25">
@@ -6338,7 +6324,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="s">
-        <v>181</v>
+        <v>9</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.25">
@@ -6346,7 +6332,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.25">
@@ -6354,7 +6340,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="s">
-        <v>168</v>
+        <v>194</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.25">
@@ -6362,7 +6348,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.25">
@@ -6370,7 +6356,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.25">
@@ -6378,7 +6364,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.25">
@@ -6386,7 +6372,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.25">
@@ -6394,7 +6380,7 @@
         <v>540</v>
       </c>
       <c r="B541" t="s">
-        <v>209</v>
+        <v>101</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.25">
@@ -6402,7 +6388,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.25">
@@ -6410,7 +6396,7 @@
         <v>542</v>
       </c>
       <c r="B543" t="s">
-        <v>35</v>
+        <v>211</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.25">
@@ -6418,7 +6404,7 @@
         <v>543</v>
       </c>
       <c r="B544" t="s">
-        <v>211</v>
+        <v>52</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.25">
@@ -6426,7 +6412,7 @@
         <v>544</v>
       </c>
       <c r="B545" t="s">
-        <v>52</v>
+        <v>508</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.25">
@@ -6434,7 +6420,7 @@
         <v>545</v>
       </c>
       <c r="B546" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.25">
@@ -6442,7 +6428,7 @@
         <v>546</v>
       </c>
       <c r="B547" t="s">
-        <v>492</v>
+        <v>90</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.25">
@@ -6450,7 +6436,7 @@
         <v>547</v>
       </c>
       <c r="B548" t="s">
-        <v>90</v>
+        <v>307</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.25">
@@ -6458,21 +6444,18 @@
         <v>548</v>
       </c>
       <c r="B549" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>549</v>
       </c>
-      <c r="B550" t="s">
-        <v>306</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B550">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B2:B549">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/Normalization/Author.xlsx
+++ b/Normalization/Author.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\peggy\Github\databaseproject-G9\Normalization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894280FB-F7EF-407A-A25B-36D52B7B0030}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED0EDE5-9817-4C19-8DFE-2AE5C8954C8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1779,8 +1779,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}" name="工作表1__210122" displayName="工作表1__210122" ref="A1:B550" totalsRowShown="0">
-  <autoFilter ref="A1:B550" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}" name="工作表1__210122" displayName="工作表1__210122" ref="A1:B549" totalsRowShown="0">
+  <autoFilter ref="A1:B549" xr:uid="{0D9F681A-B30D-4CDE-BDCF-EDDF68CB760B}"/>
   <tableColumns count="2">
     <tableColumn id="14" xr3:uid="{46B9DB32-F916-48A1-914E-F861B7933414}" name="作者代號"/>
     <tableColumn id="2" xr3:uid="{D69DDAD9-7089-4BC9-81EE-03C28CACB005}" name="作者"/>
@@ -2052,7 +2052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E78CC39A-B9B8-43E6-9805-5B697852D62F}">
-  <dimension ref="A1:B550"/>
+  <dimension ref="A1:B549"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -6445,11 +6445,6 @@
       </c>
       <c r="B549" t="s">
         <v>306</v>
-      </c>
-    </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A550">
-        <v>549</v>
       </c>
     </row>
   </sheetData>
